--- a/docs/Bang-Gia-Banh-Phu-The.xlsx
+++ b/docs/Bang-Gia-Banh-Phu-The.xlsx
@@ -8,15 +8,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t>BẢNG GIÁ DỰ ÁN BÁNH PHU THÊ — EMAGAZINE INTERACTIVE</t>
   </si>
   <si>
-    <t>5 chương + Setup + Polish  |  Trạng thái: ĐÃ HOÀN THÀNH</t>
-  </si>
-  <si>
-    <t>TỔNG: 1.295.000 VNĐ  (Giảm trừ: -170.000 VNĐ)</t>
+    <t>5 chương + Ảnh bìa + Hoàn thiện  |  ĐÃ HOÀN THÀNH TOÀN BỘ</t>
+  </si>
+  <si>
+    <t>THANH TOÁN: 1.000.000 VNĐ</t>
   </si>
   <si>
     <t>STT</t>
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>PHASE 1 — SETUP &amp; ẢNH COVER</t>
+    <t>GIAI ĐOẠN 1 — ẢNH BÌA</t>
   </si>
   <si>
     <t>Đã xong</t>
@@ -52,10 +52,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>Ảnh cover + Tích hợp Shorthand</t>
-  </si>
-  <si>
-    <t>Thiết kế ảnh cover, tích hợp cơ chế chuyển cảnh đổi màu sắc</t>
+    <t>Thiết kế ảnh bìa + tích hợp Shorthand</t>
+  </si>
+  <si>
+    <t>Thiết kế ảnh bìa 16:9, tích hợp cơ chế chuyển cảnh đổi màu sắc, responsive trên mọi thiết bị</t>
   </si>
   <si>
     <t>Dễ</t>
@@ -64,253 +64,295 @@
     <t>0.5 ngày</t>
   </si>
   <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>GIAI ĐOẠN 2 — CHƯƠNG I: NGUỒN GỐC</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Cuộn trình chiếu 5 ảnh (Scrollmation)</t>
+  </si>
+  <si>
+    <t>Hiệu ứng cuộn sticky: 5 ảnh cross-fade tự động khi cuộn trang, Ken Burns zoom nhẹ tạo cảm giác điện ảnh</t>
+  </si>
+  <si>
+    <t>Trung bình</t>
+  </si>
+  <si>
+    <t>2 ngày</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5 khối nội dung văn bản</t>
+  </si>
+  <si>
+    <t>Chuyển cảnh fade/slide mượt mà giữa các phần text, chữ tự hiện ra khi người dùng cuộn đến</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Thiết kế chữ + bố cục tạp chí</t>
+  </si>
+  <si>
+    <t>Font chữ responsive co giãn tự động, bố cục văn bản bên trái + ảnh bên phải có viền trang trí</t>
+  </si>
+  <si>
+    <t>1 ngày</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>GIAI ĐOẠN 3 — CHƯƠNG II: NGHỆ THUẬT</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Trò chơi Ngũ Hành tương tác</t>
+  </si>
+  <si>
+    <t>5 nguyên tố Mộc/Kim/Thổ/Hỏa/Thủy xoay quanh trung tâm, bấm vào hiện giải thích ý nghĩa, vòng tròn tiến trình SVG</t>
+  </si>
+  <si>
+    <t>Khó</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Hoạt ảnh bóc bánh 7 lớp</t>
+  </si>
+  <si>
+    <t>7 lớp ảnh chồng lên nhau mô phỏng quá trình bóc bánh, hiệu ứng canvas nước, animation từ lá dong vào đến nhân bánh</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Trích dẫn nghệ nhân</t>
+  </si>
+  <si>
+    <t>Ảnh trích dẫn toàn màn hình, hiệu ứng hiện ra khi cuộn + parallax lớp nền</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>GIAI ĐOẠN 4 — CHƯƠNG III: KỸ NGHỆ</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Thư viện ảnh 3 bố cục</t>
+  </si>
+  <si>
+    <t>Ba layout ảnh: lưới 3 cột nguyên liệu, bố cục 4 ảnh vỏ bánh, lưới 2 cột tạo hình — hơn 20 hiệu ứng entrance</t>
+  </si>
+  <si>
+    <t>65000</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Hiệu ứng lau ảnh + Song song + Bộ ba</t>
+  </si>
+  <si>
+    <t>Hiệu ứng lau sticky clip-path, bố cục song song lens/cine reveal, bộ ba 3 ảnh + đoạn văn</t>
+  </si>
+  <si>
+    <t>1.5 ngày</t>
+  </si>
+  <si>
     <t>50000</t>
   </si>
   <si>
-    <t>PHASE 2 — CHƯƠNG I: NGUỒN GỐC</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Hiệu ứng cuộn trình chiếu</t>
-  </si>
-  <si>
-    <t>Scrollmation sticky background + cross-fade 5 slides + Ken Burns</t>
-  </si>
-  <si>
-    <t>Trung bình</t>
-  </si>
-  <si>
-    <t>2 ngày</t>
-  </si>
-  <si>
-    <t>120000</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Chuyển cảnh giữa các phần</t>
-  </si>
-  <si>
-    <t>Fade + slide transition giữa scrollmation panels</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Video nhấp để tải x2</t>
+  </si>
+  <si>
+    <t>Nhấp placeholder load video Google Drive, hiệu ứng overlay điện ảnh: viền tối, hạt phim, đường quét, bụi nổi, góc trang trí</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Phân cảnh văn bản + Cảnh kết chương</t>
+  </si>
+  <si>
+    <t>3 khối văn bản với đường kẻ đỏ animation, cảnh Thanh Pham dramatic reveal</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Divider chương + Hệ thống cuộn</t>
+  </si>
+  <si>
+    <t>Ảnh divider toàn màn hình, IntersectionObserver kiểm soát 16 phân cảnh, stagger delays, reduced motion</t>
+  </si>
+  <si>
+    <t>GIAI ĐOẠN 5 — CHƯƠNG IV: ĐƯƠNG ĐẠI</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Thanh trượt So sánh Xưa — Nay</t>
+  </si>
+  <si>
+    <t>Kéo thanh trượt so sánh ảnh cưới truyền thống và hiện đại, hỗ trợ chuột + cảm ứng, hiệu ứng clip-path</t>
   </si>
   <si>
     <t>40000</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Thiết kế typography</t>
-  </si>
-  <si>
-    <t>Font DNS Gibsons One, responsive clamp(), animated text reveals</t>
-  </si>
-  <si>
-    <t>30000</t>
-  </si>
-  <si>
-    <t>PHASE 3 — CHƯƠNG II: NGHỆ THUẬT</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Trò chơi Ngũ Hành</t>
-  </si>
-  <si>
-    <t>5 nguyên tố Mộc/Kim/Thổ/Hỏa/Thủy, tap → hiển thị ý nghĩa</t>
-  </si>
-  <si>
-    <t>Khó</t>
-  </si>
-  <si>
-    <t>150000</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Hoạt ảnh bóc bánh</t>
-  </si>
-  <si>
-    <t>7 frame layers + canvas FX, animation bóc từng lớp</t>
-  </si>
-  <si>
-    <t>1.5 ngày</t>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Trình xem mô hình 3D (Three.js)</t>
+  </si>
+  <si>
+    <t>Công nghệ WebGL: xoay mô hình 360 độ bằng chuột/cảm ứng, 2 mô hình, tự xoay, lazy load, 3 đèn chiếu</t>
+  </si>
+  <si>
+    <t>2.5 ngày</t>
   </si>
   <si>
     <t>100000</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Trích dẫn Nghệ nhân</t>
-  </si>
-  <si>
-    <t>Quote image overlay full-bleed, scroll-driven reveal</t>
-  </si>
-  <si>
-    <t>PHASE 4 — CHƯƠNG III: KỸ NGHỆ</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Sơ đồ 6 bước vòng tròn</t>
-  </si>
-  <si>
-    <t>Process circle layout, scroll-triggered steps, mobile responsive cột dọc</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Tích hợp video cuộn</t>
-  </si>
-  <si>
-    <t>Scroll-driven video playback, lazy load, custom controls</t>
-  </si>
-  <si>
-    <t>1 ngày</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Chuyển cảnh sang Chương IV</t>
-  </si>
-  <si>
-    <t>Wipe/fade transition effect</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>PHASE 5 — CHƯƠNG IV: ĐƯƠNG ĐẠI</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Thanh trượt Trước — Sau</t>
-  </si>
-  <si>
-    <t>Before/after slider, mobile tab mode</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Hiệu ứng 3D bánh Minh Thu</t>
-  </si>
-  <si>
-    <t>Three.js 3D model, scroll-driven rotation</t>
-  </si>
-  <si>
-    <t>180000</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>So sánh ảnh xưa — nay</t>
-  </si>
-  <si>
-    <t>Dual image layout với scroll reveal xen kẽ</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Chuyển cảnh sang Chương V</t>
-  </si>
-  <si>
-    <t>PHASE 6 — CHƯƠNG V: BẢO TỒN</t>
-  </si>
-  <si>
     <t>15</t>
   </si>
   <si>
-    <t>Trình phát nhạc tùy chỉnh</t>
-  </si>
-  <si>
-    <t>Audio player + waveform + lyrics sync + play/pause</t>
+    <t>Đường dẫn SVG cuộn</t>
+  </si>
+  <si>
+    <t>Khi cuộn trang bánh di chuyển theo đường cong SVG, đường kẻ tự vẽ, cross-fade truyền thống→hiện đại, 8 ảnh gallery 4 góc</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>Hoạt ảnh parallax 4 khung</t>
-  </si>
-  <si>
-    <t>Multi-layer scroll parallax, cinematic depth effect</t>
+    <t>6 bố cục nội dung + hiệu ứng</t>
+  </si>
+  <si>
+    <t>Sáu phần: Biểu tượng / Hạnh phúc / Vùng miền / Công thức / Hương vị / Cân bằng — mỗi phần hiệu ứng entrance riêng</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>Cảnh kết thúc</t>
-  </si>
-  <si>
-    <t>Closing scene + transition fade out</t>
-  </si>
-  <si>
-    <t>PHASE 7 — HOÀN CHỈNH &amp; KIỂM TRA</t>
+    <t>Divider + Responsive</t>
+  </si>
+  <si>
+    <t>Divider toàn màn hình, responsive tablet + mobile, hover zoom, reduced motion</t>
+  </si>
+  <si>
+    <t>GIAI ĐOẠN 6 — CHƯƠNG V: BẢO TỒN</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
+    <t>So sánh cuộn ngang (Swipe)</t>
+  </si>
+  <si>
+    <t>Cuộn before/after: clip-path + đường sáng swipe line + nhãn hiện khi đạt 50%</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Thư viện ảnh cuộn</t>
+  </si>
+  <si>
+    <t>Ảnh toàn bleeds: 1 ảnh full-width + 2 ảnh cạnh nhau, 3 hiệu ứng entrance riêng biệt</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Văn bản + Ảnh minh họa + Thơ</t>
+  </si>
+  <si>
+    <t>Hiệu ứng slide-left + zoom-in cho ảnh, 3 đoạn văn, trích dẫn thơ, ca dao dân gian</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Ảnh nghệ nhân + Lightbox</t>
+  </si>
+  <si>
+    <t>Hiệu ứng cinematic reveal, lightbox overlay xem ảnh phóng to, grid 8 hiệu ứng entrance</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Divider + Closing chương</t>
+  </si>
+  <si>
+    <t>Divider + đoạn kết + đường kẻ trang trí gradient + thơ dân gian typography</t>
+  </si>
+  <si>
+    <t>GIAI ĐOẠN 7 — HOÀN CHỈNH &amp; KIỂM TRA</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>Responsive mọi thiết bị</t>
   </si>
   <si>
-    <t>Layout mobile 375px / tablet 768px / desktop 1440px</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>Điện thoại 375px / tablet 768px / desktop 1440px, bố cục co giãn, hỗ trợ cảm ứng</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>Tối ưu hiệu năng</t>
   </si>
   <si>
-    <t>Tối ưu ảnh WebP, preload font, Lighthouse score</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>Chuyển ảnh WebP, content-visibility, lazy load, preload font, render loop theo visibility</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>Sửa lỗi &amp; tương thích</t>
   </si>
   <si>
-    <t>Cross-browser testing, scroll jank fix, accessibility</t>
-  </si>
-  <si>
-    <t>Tổng cộng</t>
-  </si>
-  <si>
-    <t>1.465.000</t>
-  </si>
-  <si>
-    <t>Giảm trừ (không artwork)</t>
-  </si>
-  <si>
-    <t>-170.000</t>
-  </si>
-  <si>
-    <t>THANH TOÁN</t>
-  </si>
-  <si>
-    <t>1.295.000</t>
+    <t>Cross-browser, sửa scroll jank, reduced-motion accessibility, font fallback</t>
+  </si>
+  <si>
+    <t>TỔNG CỘNG</t>
+  </si>
+  <si>
+    <t>1.000.000</t>
   </si>
 </sst>
 </file>
@@ -353,11 +395,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -366,8 +406,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="85" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -579,18 +619,18 @@
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -599,7 +639,7 @@
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -665,24 +705,24 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
         <v>43</v>
-      </c>
-      <c r="G14" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
@@ -694,7 +734,7 @@
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -734,208 +774,208 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
         <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
         <v>70</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
         <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>74</v>
       </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -944,90 +984,90 @@
         <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
@@ -1036,21 +1076,21 @@
         <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
@@ -1059,21 +1099,21 @@
         <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
@@ -1082,80 +1122,149 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" t="s">
         <v>17</v>
       </c>
-      <c r="G32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="G33" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="34">
       <c r="A34" t="s">
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G35" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>100</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
